--- a/site/exports/tju-humanities-arts.xlsx
+++ b/site/exports/tju-humanities-arts.xlsx
@@ -1257,7 +1257,7 @@
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L7" s="2" t="b">
@@ -1328,7 +1328,7 @@
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr"/>
@@ -1397,7 +1397,7 @@
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1828,7 +1828,7 @@
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="L16" s="2" t="b">
